--- a/Results/- Resultados.xlsx
+++ b/Results/- Resultados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23FF86C-2E79-418D-A92A-B7F24E819EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4927843D-8C71-4727-9BE0-080E33310B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
@@ -20,11 +20,11 @@
     <sheet name="ParkDatabase" sheetId="19" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MountainDatabase!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">WashingtonDatabase!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LennaDatabase!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MountainDatabase!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PalaceDatabase!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ParkDatabase!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">WashingtonDatabase!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="70">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>CP Hash Hamming</t>
-  </si>
-  <si>
-    <t>Hsv-Color Hamming</t>
   </si>
   <si>
     <t>Média 3x3</t>
@@ -293,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,12 +324,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -436,10 +427,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -453,10 +444,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -464,7 +452,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -474,13 +462,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1240,7 +1228,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>LennaDatabase!$G$1</c:f>
+              <c:f>LennaDatabase!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1345,11 +1333,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$G$2:$G$21</c15:sqref>
+                    <c15:sqref>LennaDatabase!$F$2:$F$21</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>LennaDatabase!$G$3:$G$21</c:f>
+              <c:f>LennaDatabase!$F$3:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
@@ -1443,25 +1431,18 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>LennaDatabase!$F$1</c15:sqref>
+                          <c15:sqref>LennaDatabase!#REF!</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>Hsv-Color Hamming</c:v>
+                        <c:v>#REF!</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
                 </c:tx>
-                <c:spPr>
-                  <a:ln>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6"/>
-                    </a:solidFill>
-                  </a:ln>
-                </c:spPr>
                 <c:marker>
                   <c:spPr>
                     <a:solidFill>
@@ -1553,73 +1534,16 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>LennaDatabase!$F$2:$F$21</c15:sqref>
+                          <c15:sqref>LennaDatabase!#REF!</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>LennaDatabase!$F$3:$F$21</c15:sqref>
+                          <c15:sqref>LennaDatabase!#REF!</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="19"/>
-                      <c:pt idx="0">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>4</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>5</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>2</c:v>
-                      </c:pt>
+                      <c:ptCount val="0"/>
                     </c:numCache>
                   </c:numRef>
                 </c:val>
@@ -2288,7 +2212,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>WashingtonDatabase!$G$1</c:f>
+              <c:f>WashingtonDatabase!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2354,11 +2278,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>WashingtonDatabase!$G$2:$G$8</c15:sqref>
+                    <c15:sqref>WashingtonDatabase!$F$2:$F$8</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>WashingtonDatabase!$G$3:$G$8</c:f>
+              <c:f>WashingtonDatabase!$F$3:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2413,25 +2337,18 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>WashingtonDatabase!$F$1</c15:sqref>
+                          <c15:sqref>WashingtonDatabase!#REF!</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>Hsv-Color Hamming</c:v>
+                        <c:v>#REF!</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
                 </c:tx>
-                <c:spPr>
-                  <a:ln>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6"/>
-                    </a:solidFill>
-                  </a:ln>
-                </c:spPr>
                 <c:marker>
                   <c:spPr>
                     <a:solidFill>
@@ -2484,34 +2401,16 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>WashingtonDatabase!$F$2:$F$8</c15:sqref>
+                          <c15:sqref>WashingtonDatabase!#REF!</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>WashingtonDatabase!$F$3:$F$8</c15:sqref>
+                          <c15:sqref>WashingtonDatabase!#REF!</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>1</c:v>
-                      </c:pt>
+                      <c:ptCount val="0"/>
                     </c:numCache>
                   </c:numRef>
                 </c:val>
@@ -2872,14 +2771,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>WashingtonDatabase!$A$37:$A$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(WashingtonDatabase!$A$37:$A$40,WashingtonDatabase!$A$42)</c:f>
+              <c:f>WashingtonDatabase!$A$37:$A$41</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -2902,14 +2794,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>WashingtonDatabase!$B$37:$B$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(WashingtonDatabase!$B$37:$B$40,WashingtonDatabase!$B$42)</c:f>
+              <c:f>WashingtonDatabase!$B$37:$B$41</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3280,14 +3165,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>WashingtonDatabase!$A$37:$A$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(WashingtonDatabase!$A$37:$A$40,WashingtonDatabase!$A$42)</c:f>
+              <c:f>WashingtonDatabase!$A$37:$A$41</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3310,14 +3188,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>WashingtonDatabase!$C$37:$C$42</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(WashingtonDatabase!$C$37:$C$40,WashingtonDatabase!$C$42)</c:f>
+              <c:f>WashingtonDatabase!$C$37:$C$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -4035,22 +3906,15 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>ParkDatabase!$F$1</c:f>
+              <c:f>ParkDatabase!#REF!</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Hsv-Color Hamming</c:v>
+                  <c:v>#REF!</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
           <c:marker>
             <c:spPr>
               <a:solidFill>
@@ -4103,38 +3967,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ParkDatabase!$F$3:$F$12</c:f>
+              <c:f>ParkDatabase!#REF!</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4152,7 +3989,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>ParkDatabase!$G$1</c:f>
+              <c:f>ParkDatabase!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4220,7 +4057,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ParkDatabase!$G$3:$G$12</c:f>
+              <c:f>ParkDatabase!$F$3:$F$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4623,14 +4460,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>ParkDatabase!$A$43:$A$48</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(ParkDatabase!$A$43:$A$46,ParkDatabase!$A$48)</c:f>
+              <c:f>ParkDatabase!$A$43:$A$47</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -4653,14 +4483,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>ParkDatabase!$B$43:$B$48</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(ParkDatabase!$B$43:$B$46,ParkDatabase!$B$48)</c:f>
+              <c:f>ParkDatabase!$B$43:$B$47</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -5031,14 +4854,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>ParkDatabase!$A$43:$A$48</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(ParkDatabase!$A$43:$A$46,ParkDatabase!$A$48)</c:f>
+              <c:f>ParkDatabase!$A$43:$A$47</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -5061,14 +4877,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>ParkDatabase!$C$43:$C$48</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(ParkDatabase!$C$43:$C$46,ParkDatabase!$C$48)</c:f>
+              <c:f>ParkDatabase!$C$43:$C$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -5497,14 +5306,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$A$51:$A$56</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(LennaDatabase!$A$51:$A$54,LennaDatabase!$A$56)</c:f>
+              <c:f>LennaDatabase!$A$51:$A$55</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -5527,14 +5329,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$B$51:$B$56</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(LennaDatabase!$B$51:$B$54,LennaDatabase!$B$56)</c:f>
+              <c:f>LennaDatabase!$B$51:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -5964,14 +5759,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$A$51:$A$56</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(LennaDatabase!$A$51:$A$54,LennaDatabase!$A$56)</c:f>
+              <c:f>LennaDatabase!$A$51:$A$55</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -5994,14 +5782,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>LennaDatabase!$C$51:$C$56</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(LennaDatabase!$C$51:$C$54,LennaDatabase!$C$56)</c:f>
+              <c:f>LennaDatabase!$C$51:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -7175,22 +6956,15 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>MountainDatabase!$F$1</c:f>
+              <c:f>MountainDatabase!#REF!</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Hsv-Color Hamming</c:v>
+                  <c:v>#REF!</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
           <c:marker>
             <c:spPr>
               <a:solidFill>
@@ -7300,96 +7074,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MountainDatabase!$F$3:$F$31</c:f>
+              <c:f>MountainDatabase!#REF!</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7406,7 +7096,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>MountainDatabase!$G$1</c:f>
+              <c:f>MountainDatabase!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7531,7 +7221,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MountainDatabase!$G$3:$G$31</c:f>
+              <c:f>MountainDatabase!$F$3:$F$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
@@ -7991,14 +7681,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$62:$A$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$A$62:$A$65,MountainDatabase!$A$67)</c:f>
+              <c:f>MountainDatabase!$A$62:$A$66</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -8021,14 +7704,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$B$62:$B$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$B$62:$B$65,MountainDatabase!$B$67)</c:f>
+              <c:f>MountainDatabase!$B$62:$B$66</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -8399,14 +8075,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$A$62:$A$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$A$62:$A$65,MountainDatabase!$A$67)</c:f>
+              <c:f>MountainDatabase!$A$62:$A$66</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -8429,14 +8098,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>MountainDatabase!$C$62:$C$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(MountainDatabase!$C$62:$C$65,MountainDatabase!$C$67)</c:f>
+              <c:f>MountainDatabase!$C$62:$C$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -9610,22 +9272,15 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>PalaceDatabase!$F$1</c:f>
+              <c:f>PalaceDatabase!#REF!</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Hsv-Color Hamming</c:v>
+                  <c:v>#REF!</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
           <c:marker>
             <c:spPr>
               <a:solidFill>
@@ -9735,96 +9390,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PalaceDatabase!$F$3:$F$31</c:f>
+              <c:f>PalaceDatabase!#REF!</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9841,7 +9412,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>PalaceDatabase!$G$1</c:f>
+              <c:f>PalaceDatabase!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9966,7 +9537,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PalaceDatabase!$G$3:$G$31</c:f>
+              <c:f>PalaceDatabase!$F$3:$F$31</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="29"/>
@@ -10426,14 +9997,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>PalaceDatabase!$A$62:$A$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(PalaceDatabase!$A$62:$A$65,PalaceDatabase!$A$67)</c:f>
+              <c:f>PalaceDatabase!$A$62:$A$66</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -10456,14 +10020,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>PalaceDatabase!$B$62:$B$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(PalaceDatabase!$B$62:$B$65,PalaceDatabase!$B$67)</c:f>
+              <c:f>PalaceDatabase!$B$62:$B$66</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -10834,14 +10391,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>PalaceDatabase!$A$62:$A$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(PalaceDatabase!$A$62:$A$65,PalaceDatabase!$A$67)</c:f>
+              <c:f>PalaceDatabase!$A$62:$A$66</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -10864,14 +10414,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>PalaceDatabase!$C$62:$C$67</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>(PalaceDatabase!$C$62:$C$65,PalaceDatabase!$C$67)</c:f>
+              <c:f>PalaceDatabase!$C$62:$C$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -10882,7 +10425,7 @@
                   <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>75</c:v>
@@ -10982,7 +10525,7 @@
         <c:axId val="1631798208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="450"/>
+          <c:max val="460"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -16697,8 +16240,8 @@
       <xdr:rowOff>137583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>10584</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:to>
@@ -16731,13 +16274,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>920750</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -16768,14 +16311,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1043121</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:colOff>1043120</xdr:colOff>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>189180</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>709083</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:colOff>1280582</xdr:colOff>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -16816,7 +16359,7 @@
       <xdr:rowOff>74083</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>592667</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>109803</xdr:rowOff>
@@ -16850,13 +16393,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>177271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -16888,13 +16431,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>9263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>172381</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -16935,7 +16478,7 @@
       <xdr:rowOff>188383</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>592667</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -16969,13 +16512,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>177271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17007,13 +16550,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>9263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>172381</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17049,13 +16592,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>97896</xdr:colOff>
+      <xdr:colOff>97895</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>137583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>42334</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>592665</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
@@ -17088,13 +16631,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>169334</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>119987</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>381001</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>92605</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17125,14 +16668,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>588037</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:colOff>588036</xdr:colOff>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>115096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>317501</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>232832</xdr:colOff>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>87714</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17173,7 +16716,7 @@
       <xdr:rowOff>74083</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>592667</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>109803</xdr:rowOff>
@@ -17207,13 +16750,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>14153</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>328084</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>177271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17245,13 +16788,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>693870</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>9263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>423332</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>172381</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17579,7 +17122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
@@ -17587,12 +17130,11 @@
     <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -17609,13 +17151,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -17634,426 +17173,369 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="20">
         <v>0</v>
       </c>
+      <c r="C3" s="20">
+        <v>0</v>
+      </c>
+      <c r="D3" s="20">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0</v>
+      </c>
+      <c r="F3" s="21">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="21">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="20">
         <v>0</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D4" s="20">
         <v>0</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E4" s="20">
         <v>0</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F4" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="20">
         <v>0</v>
       </c>
-      <c r="G3" s="22">
+      <c r="C5" s="20">
+        <v>0</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="20">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0</v>
+      </c>
+      <c r="D6" s="20">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="20">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="20">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20">
+        <v>0</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="20">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="20">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20">
+        <v>0</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="20">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="20">
+        <v>1</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20">
+        <v>3</v>
+      </c>
+      <c r="C13" s="20">
+        <v>2</v>
+      </c>
+      <c r="D13" s="20">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="20">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0</v>
+      </c>
+      <c r="D14" s="20">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
+      <c r="F14" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="20">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20">
+        <v>2</v>
+      </c>
+      <c r="F15" s="21">
+        <v>13.625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="20">
+        <v>0</v>
+      </c>
+      <c r="C16" s="19">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19">
+        <v>2</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="20">
+        <v>10</v>
+      </c>
+      <c r="C17" s="20">
+        <v>8</v>
+      </c>
+      <c r="D17" s="20">
+        <v>2</v>
+      </c>
+      <c r="E17" s="20">
+        <v>6</v>
+      </c>
+      <c r="F17" s="21">
+        <v>12.875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="20">
         <v>7</v>
       </c>
-      <c r="B4" s="21">
-        <v>0</v>
-      </c>
-      <c r="C4" s="21">
-        <v>0</v>
-      </c>
-      <c r="D4" s="21">
-        <v>0</v>
-      </c>
-      <c r="E4" s="21">
-        <v>0</v>
-      </c>
-      <c r="F4" s="21">
-        <v>0</v>
-      </c>
-      <c r="G4" s="22">
-        <v>0.5</v>
+      <c r="C18" s="20">
+        <v>10</v>
+      </c>
+      <c r="D18" s="20">
+        <v>5</v>
+      </c>
+      <c r="E18" s="20">
+        <v>5</v>
+      </c>
+      <c r="F18" s="21">
+        <v>13.125</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="20">
+        <v>14</v>
+      </c>
+      <c r="C19" s="20">
+        <v>10</v>
+      </c>
+      <c r="D19" s="20">
         <v>8</v>
       </c>
-      <c r="B5" s="21">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21">
-        <v>0</v>
-      </c>
-      <c r="E5" s="21">
-        <v>0</v>
-      </c>
-      <c r="F5" s="21">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0.5</v>
+      <c r="E19" s="20">
+        <v>14</v>
+      </c>
+      <c r="F19" s="21">
+        <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="21">
-        <v>0</v>
-      </c>
-      <c r="C6" s="21">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21">
-        <v>0</v>
-      </c>
-      <c r="E6" s="21">
-        <v>0</v>
-      </c>
-      <c r="F6" s="21">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.875</v>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="20">
+        <v>14</v>
+      </c>
+      <c r="C20" s="20">
+        <v>16</v>
+      </c>
+      <c r="D20" s="20">
+        <v>14</v>
+      </c>
+      <c r="E20" s="20">
+        <v>14</v>
+      </c>
+      <c r="F20" s="21">
+        <v>14.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="21">
-        <v>0</v>
-      </c>
-      <c r="C7" s="21">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22">
-        <v>1.125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="21">
-        <v>0</v>
-      </c>
-      <c r="C8" s="21">
-        <v>0</v>
-      </c>
-      <c r="D8" s="21">
-        <v>0</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="21">
-        <v>0</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="21">
-        <v>0</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22">
-        <v>2.875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="21">
-        <v>0</v>
-      </c>
-      <c r="C11" s="21">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0</v>
-      </c>
-      <c r="G11" s="22">
-        <v>2.875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="21">
-        <v>1</v>
-      </c>
-      <c r="C12" s="20">
-        <v>0</v>
-      </c>
-      <c r="D12" s="20">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20">
-        <v>0</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0</v>
-      </c>
-      <c r="G12" s="22">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="21">
-        <v>3</v>
-      </c>
-      <c r="C13" s="21">
-        <v>2</v>
-      </c>
-      <c r="D13" s="21">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21">
-        <v>1</v>
-      </c>
-      <c r="G13" s="22">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="21">
-        <v>0</v>
-      </c>
-      <c r="C14" s="21">
-        <v>0</v>
-      </c>
-      <c r="D14" s="21">
-        <v>0</v>
-      </c>
-      <c r="E14" s="21">
-        <v>0</v>
-      </c>
-      <c r="F14" s="21">
-        <v>4</v>
-      </c>
-      <c r="G14" s="22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="21">
-        <v>0</v>
-      </c>
-      <c r="C15" s="21">
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
-        <v>1</v>
-      </c>
-      <c r="E15" s="21">
-        <v>2</v>
-      </c>
-      <c r="F15" s="21">
-        <v>2</v>
-      </c>
-      <c r="G15" s="22">
-        <v>13.625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="21">
-        <v>0</v>
-      </c>
-      <c r="C16" s="20">
-        <v>0</v>
-      </c>
-      <c r="D16" s="20">
-        <v>2</v>
-      </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
-      <c r="F16" s="20">
-        <v>1</v>
-      </c>
-      <c r="G16" s="22">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="21">
-        <v>10</v>
-      </c>
-      <c r="C17" s="21">
-        <v>8</v>
-      </c>
-      <c r="D17" s="21">
-        <v>2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>6</v>
-      </c>
-      <c r="F17" s="21">
-        <v>0</v>
-      </c>
-      <c r="G17" s="22">
-        <v>12.875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="21">
-        <v>7</v>
-      </c>
-      <c r="C18" s="21">
-        <v>10</v>
-      </c>
-      <c r="D18" s="21">
-        <v>5</v>
-      </c>
-      <c r="E18" s="21">
-        <v>5</v>
-      </c>
-      <c r="F18" s="21">
-        <v>5</v>
-      </c>
-      <c r="G18" s="22">
-        <v>13.125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="21">
-        <v>14</v>
-      </c>
-      <c r="C19" s="21">
-        <v>10</v>
-      </c>
-      <c r="D19" s="21">
-        <v>8</v>
-      </c>
-      <c r="E19" s="21">
-        <v>14</v>
-      </c>
-      <c r="F19" s="21">
-        <v>1</v>
-      </c>
-      <c r="G19" s="22">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="21">
-        <v>14</v>
-      </c>
-      <c r="C20" s="21">
-        <v>16</v>
-      </c>
-      <c r="D20" s="21">
-        <v>14</v>
-      </c>
-      <c r="E20" s="21">
-        <v>14</v>
-      </c>
-      <c r="F20" s="21">
-        <v>0</v>
-      </c>
-      <c r="G20" s="22">
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B21" s="1">
@@ -18068,29 +17550,26 @@
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="F21" s="18">
         <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="23">
         <v>24.494897427831699</v>
       </c>
       <c r="C51" s="1">
@@ -18101,7 +17580,7 @@
       <c r="A52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="23">
         <v>23.664319132398401</v>
       </c>
       <c r="C52" s="1">
@@ -18112,7 +17591,7 @@
       <c r="A53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B53" s="23">
         <v>17.8605710994917</v>
       </c>
       <c r="C53" s="1">
@@ -18123,7 +17602,7 @@
       <c r="A54" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="23">
         <v>22.203603311174501</v>
       </c>
       <c r="C54" s="1">
@@ -18132,30 +17611,19 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" s="24">
-        <v>7.2111025509279703</v>
-      </c>
-      <c r="C55" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B55" s="23">
         <v>36.681120484521699</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C55" s="17">
         <v>109.92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
-      <sortCondition ref="G1"/>
+  <autoFilter ref="A1:F21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+      <sortCondition ref="F1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -18167,7 +17635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1700E9-6CDB-4501-8AE5-13FB0E8EAE79}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -18175,12 +17643,11 @@
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -18197,13 +17664,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -18222,427 +17686,370 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="20">
         <v>0</v>
       </c>
+      <c r="C3" s="20">
+        <v>2</v>
+      </c>
+      <c r="D3" s="20">
+        <v>2</v>
+      </c>
+      <c r="E3" s="20">
+        <v>2</v>
+      </c>
+      <c r="F3" s="21">
+        <v>14.16</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B4" s="20">
         <v>0</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C4" s="20">
         <v>2</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D4" s="20">
+        <v>1</v>
+      </c>
+      <c r="E4" s="20">
         <v>2</v>
       </c>
-      <c r="E3" s="21">
+      <c r="F4" s="20">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="20">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
         <v>2</v>
       </c>
-      <c r="F3" s="21">
+      <c r="D5" s="20">
+        <v>1</v>
+      </c>
+      <c r="E5" s="20">
+        <v>2</v>
+      </c>
+      <c r="F5" s="21">
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="20">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20">
+        <v>2</v>
+      </c>
+      <c r="D6" s="20">
+        <v>2</v>
+      </c>
+      <c r="E6" s="20">
+        <v>2</v>
+      </c>
+      <c r="F6" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="20">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20">
+        <v>2</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
+      <c r="E7" s="20">
+        <v>2</v>
+      </c>
+      <c r="F7" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="20">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20">
+        <v>2</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
+      </c>
+      <c r="E8" s="20">
+        <v>2</v>
+      </c>
+      <c r="F8" s="21">
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="20">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20">
+        <v>2</v>
+      </c>
+      <c r="D9" s="20">
+        <v>2</v>
+      </c>
+      <c r="E9" s="20">
+        <v>2</v>
+      </c>
+      <c r="F9" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="20">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20">
+        <v>2</v>
+      </c>
+      <c r="D10" s="20">
+        <v>2</v>
+      </c>
+      <c r="E10" s="20">
+        <v>4</v>
+      </c>
+      <c r="F10" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="20">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20">
+        <v>2</v>
+      </c>
+      <c r="D11" s="20">
+        <v>1</v>
+      </c>
+      <c r="E11" s="20">
+        <v>4</v>
+      </c>
+      <c r="F11" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="20">
+        <v>0</v>
+      </c>
+      <c r="C12" s="19">
+        <v>2</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1</v>
+      </c>
+      <c r="E12" s="19">
+        <v>2</v>
+      </c>
+      <c r="F12" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="20">
+        <v>0</v>
+      </c>
+      <c r="C13" s="20">
+        <v>2</v>
+      </c>
+      <c r="D13" s="20">
+        <v>1</v>
+      </c>
+      <c r="E13" s="20">
+        <v>2</v>
+      </c>
+      <c r="F13" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="20">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20">
+        <v>2</v>
+      </c>
+      <c r="D14" s="20">
+        <v>1</v>
+      </c>
+      <c r="E14" s="20">
+        <v>2</v>
+      </c>
+      <c r="F14" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="20">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20">
+        <v>4</v>
+      </c>
+      <c r="F15" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="20">
+        <v>0</v>
+      </c>
+      <c r="C16" s="19">
+        <v>2</v>
+      </c>
+      <c r="D16" s="19">
+        <v>0</v>
+      </c>
+      <c r="E16" s="19">
+        <v>2</v>
+      </c>
+      <c r="F16" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="20">
+        <v>0</v>
+      </c>
+      <c r="C17" s="20">
+        <v>2</v>
+      </c>
+      <c r="D17" s="20">
+        <v>2</v>
+      </c>
+      <c r="E17" s="20">
+        <v>4</v>
+      </c>
+      <c r="F17" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="20">
+        <v>4</v>
+      </c>
+      <c r="C18" s="20">
         <v>6</v>
       </c>
-      <c r="G3" s="22">
-        <v>14.16</v>
+      <c r="D18" s="20">
+        <v>3</v>
+      </c>
+      <c r="E18" s="20">
+        <v>6</v>
+      </c>
+      <c r="F18" s="21">
+        <v>15.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="21">
-        <v>0</v>
-      </c>
-      <c r="C4" s="21">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="20">
+        <v>4</v>
+      </c>
+      <c r="C19" s="20">
+        <v>8</v>
+      </c>
+      <c r="D19" s="20">
+        <v>4</v>
+      </c>
+      <c r="E19" s="20">
+        <v>6</v>
+      </c>
+      <c r="F19" s="21">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="20">
         <v>2</v>
       </c>
-      <c r="D4" s="21">
-        <v>1</v>
-      </c>
-      <c r="E4" s="21">
-        <v>2</v>
-      </c>
-      <c r="F4" s="21">
-        <v>5</v>
-      </c>
-      <c r="G4" s="21">
-        <v>15.16</v>
+      <c r="C20" s="20">
+        <v>8</v>
+      </c>
+      <c r="D20" s="20">
+        <v>4</v>
+      </c>
+      <c r="E20" s="20">
+        <v>6</v>
+      </c>
+      <c r="F20" s="21">
+        <v>14.66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="21">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21">
-        <v>2</v>
-      </c>
-      <c r="D5" s="21">
-        <v>1</v>
-      </c>
-      <c r="E5" s="21">
-        <v>2</v>
-      </c>
-      <c r="F5" s="21">
-        <v>5</v>
-      </c>
-      <c r="G5" s="22">
-        <v>14.66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="21">
-        <v>0</v>
-      </c>
-      <c r="C6" s="21">
-        <v>2</v>
-      </c>
-      <c r="D6" s="21">
-        <v>2</v>
-      </c>
-      <c r="E6" s="21">
-        <v>2</v>
-      </c>
-      <c r="F6" s="21">
-        <v>5</v>
-      </c>
-      <c r="G6" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="21">
-        <v>0</v>
-      </c>
-      <c r="C7" s="21">
-        <v>2</v>
-      </c>
-      <c r="D7" s="21">
-        <v>1</v>
-      </c>
-      <c r="E7" s="21">
-        <v>2</v>
-      </c>
-      <c r="F7" s="21">
-        <v>4</v>
-      </c>
-      <c r="G7" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="21">
-        <v>0</v>
-      </c>
-      <c r="C8" s="21">
-        <v>2</v>
-      </c>
-      <c r="D8" s="21">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21">
-        <v>2</v>
-      </c>
-      <c r="F8" s="21">
-        <v>6</v>
-      </c>
-      <c r="G8" s="22">
-        <v>14.66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="21">
-        <v>0</v>
-      </c>
-      <c r="C9" s="21">
-        <v>2</v>
-      </c>
-      <c r="D9" s="21">
-        <v>2</v>
-      </c>
-      <c r="E9" s="21">
-        <v>2</v>
-      </c>
-      <c r="F9" s="21">
-        <v>4</v>
-      </c>
-      <c r="G9" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="21">
-        <v>0</v>
-      </c>
-      <c r="C10" s="21">
-        <v>2</v>
-      </c>
-      <c r="D10" s="21">
-        <v>2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>4</v>
-      </c>
-      <c r="F10" s="21">
-        <v>4</v>
-      </c>
-      <c r="G10" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="21">
-        <v>0</v>
-      </c>
-      <c r="C11" s="21">
-        <v>2</v>
-      </c>
-      <c r="D11" s="21">
-        <v>1</v>
-      </c>
-      <c r="E11" s="21">
-        <v>4</v>
-      </c>
-      <c r="F11" s="21">
-        <v>5</v>
-      </c>
-      <c r="G11" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="21">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20">
-        <v>2</v>
-      </c>
-      <c r="D12" s="20">
-        <v>1</v>
-      </c>
-      <c r="E12" s="20">
-        <v>2</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4</v>
-      </c>
-      <c r="G12" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="21">
-        <v>0</v>
-      </c>
-      <c r="C13" s="21">
-        <v>2</v>
-      </c>
-      <c r="D13" s="21">
-        <v>1</v>
-      </c>
-      <c r="E13" s="21">
-        <v>2</v>
-      </c>
-      <c r="F13" s="21">
-        <v>5</v>
-      </c>
-      <c r="G13" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="21">
-        <v>0</v>
-      </c>
-      <c r="C14" s="21">
-        <v>2</v>
-      </c>
-      <c r="D14" s="21">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21">
-        <v>2</v>
-      </c>
-      <c r="F14" s="21">
-        <v>5</v>
-      </c>
-      <c r="G14" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="21">
-        <v>0</v>
-      </c>
-      <c r="C15" s="21">
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
-        <v>1</v>
-      </c>
-      <c r="E15" s="21">
-        <v>4</v>
-      </c>
-      <c r="F15" s="21">
-        <v>5</v>
-      </c>
-      <c r="G15" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="21">
-        <v>0</v>
-      </c>
-      <c r="C16" s="20">
-        <v>2</v>
-      </c>
-      <c r="D16" s="20">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20">
-        <v>2</v>
-      </c>
-      <c r="F16" s="20">
-        <v>5</v>
-      </c>
-      <c r="G16" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="21">
-        <v>0</v>
-      </c>
-      <c r="C17" s="21">
-        <v>2</v>
-      </c>
-      <c r="D17" s="21">
-        <v>2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>4</v>
-      </c>
-      <c r="F17" s="21">
-        <v>5</v>
-      </c>
-      <c r="G17" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="21">
-        <v>4</v>
-      </c>
-      <c r="C18" s="21">
-        <v>6</v>
-      </c>
-      <c r="D18" s="21">
-        <v>3</v>
-      </c>
-      <c r="E18" s="21">
-        <v>6</v>
-      </c>
-      <c r="F18" s="21">
-        <v>5</v>
-      </c>
-      <c r="G18" s="22">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="21">
-        <v>4</v>
-      </c>
-      <c r="C19" s="21">
-        <v>8</v>
-      </c>
-      <c r="D19" s="21">
-        <v>4</v>
-      </c>
-      <c r="E19" s="21">
-        <v>6</v>
-      </c>
-      <c r="F19" s="21">
-        <v>4</v>
-      </c>
-      <c r="G19" s="22">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="B20" s="21">
-        <v>2</v>
-      </c>
-      <c r="C20" s="21">
-        <v>8</v>
-      </c>
-      <c r="D20" s="21">
-        <v>4</v>
-      </c>
-      <c r="E20" s="21">
-        <v>6</v>
-      </c>
-      <c r="F20" s="21">
-        <v>7</v>
-      </c>
-      <c r="G20" s="22">
-        <v>14.66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -18656,16 +18063,13 @@
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="1">
-        <v>4</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="F21" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>56</v>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -18679,16 +18083,13 @@
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="1">
-        <v>5</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="F22" s="18">
         <v>15.33</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>57</v>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="B23" s="1">
         <v>3</v>
@@ -18702,16 +18103,13 @@
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="1">
-        <v>5</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="F23" s="18">
         <v>15.33</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>58</v>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
@@ -18725,16 +18123,13 @@
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="1">
-        <v>4</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="F24" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>59</v>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
@@ -18748,16 +18143,13 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="1">
-        <v>4</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="F25" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>60</v>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
@@ -18771,16 +18163,13 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="1">
-        <v>2</v>
-      </c>
-      <c r="G26" s="19">
+      <c r="F26" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>61</v>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
@@ -18794,16 +18183,13 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="1">
-        <v>5</v>
-      </c>
-      <c r="G27" s="19">
+      <c r="F27" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>62</v>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
@@ -18817,16 +18203,13 @@
       <c r="E28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="1">
-        <v>5</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="F28" s="18">
         <v>15.66</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>63</v>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
@@ -18840,16 +18223,13 @@
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="1">
-        <v>5</v>
-      </c>
-      <c r="G29" s="19">
+      <c r="F29" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>64</v>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
@@ -18863,16 +18243,13 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="1">
-        <v>5</v>
-      </c>
-      <c r="G30" s="19">
+      <c r="F30" s="18">
         <v>15.16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>65</v>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
@@ -18886,29 +18263,26 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="1">
-        <v>3</v>
-      </c>
-      <c r="G31" s="19">
+      <c r="F31" s="18">
         <v>15.16</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62" s="14">
         <v>7.1414284285428504</v>
       </c>
       <c r="C62" s="1">
@@ -18919,7 +18293,7 @@
       <c r="A63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63" s="14">
         <v>21.166010488516701</v>
       </c>
       <c r="C63" s="1">
@@ -18930,7 +18304,7 @@
       <c r="A64" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B64" s="15">
+      <c r="B64" s="14">
         <v>12.2474487139158</v>
       </c>
       <c r="C64" s="1">
@@ -18941,7 +18315,7 @@
       <c r="A65" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65" s="14">
         <v>19.595917942265402</v>
       </c>
       <c r="C65" s="1">
@@ -18950,30 +18324,19 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B66" s="15">
-        <v>25.7293606605372</v>
-      </c>
-      <c r="C66" s="1">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="15">
+      <c r="B66" s="14">
         <v>81.406961618770595</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C66" s="17">
         <v>438.32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
-      <sortCondition ref="G1"/>
+  <autoFilter ref="A1:F21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+      <sortCondition ref="F1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -18984,7 +18347,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5E99B7-6803-4C8D-BB4A-BB3C56FEF470}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -18992,12 +18355,11 @@
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -19014,13 +18376,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -19039,427 +18398,370 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="20">
         <v>0</v>
       </c>
+      <c r="C3" s="20">
+        <v>0</v>
+      </c>
+      <c r="D3" s="20">
+        <v>2</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0</v>
+      </c>
+      <c r="F3" s="21">
+        <v>15.4</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B4" s="20">
         <v>0</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D4" s="20">
         <v>2</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E4" s="20">
         <v>0</v>
       </c>
-      <c r="F3" s="21">
-        <v>6</v>
-      </c>
-      <c r="G3" s="22">
+      <c r="F4" s="21">
         <v>15.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B5" s="20">
         <v>0</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C5" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D5" s="20">
+        <v>1</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="20">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0</v>
+      </c>
+      <c r="D6" s="20">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="20">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="20">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20">
         <v>2</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E8" s="20">
         <v>0</v>
       </c>
-      <c r="F4" s="21">
-        <v>3</v>
-      </c>
-      <c r="G4" s="22">
+      <c r="F8" s="21">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="20">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
         <v>15.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="21">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="20">
         <v>0</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C10" s="20">
         <v>0</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D10" s="20">
         <v>1</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E10" s="20">
         <v>0</v>
       </c>
-      <c r="F5" s="21">
-        <v>4</v>
-      </c>
-      <c r="G5" s="22">
+      <c r="F10" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="20">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="20">
+        <v>0</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
+        <v>2</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="20">
+        <v>0</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
+        <v>2</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="20">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0</v>
+      </c>
+      <c r="D14" s="20">
+        <v>2</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
+      <c r="F14" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="20">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="20">
+        <v>0</v>
+      </c>
+      <c r="C16" s="19">
+        <v>2</v>
+      </c>
+      <c r="D16" s="19">
+        <v>2</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21">
         <v>15.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="21">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="20">
         <v>0</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C17" s="20">
         <v>0</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D17" s="20">
+        <v>1</v>
+      </c>
+      <c r="E17" s="20">
         <v>0</v>
       </c>
-      <c r="E6" s="21">
+      <c r="F17" s="21">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="20">
         <v>0</v>
       </c>
-      <c r="F6" s="21">
-        <v>4</v>
-      </c>
-      <c r="G6" s="22">
+      <c r="C18" s="20">
+        <v>0</v>
+      </c>
+      <c r="D18" s="20">
+        <v>1</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0</v>
+      </c>
+      <c r="F18" s="21">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="20">
+        <v>10</v>
+      </c>
+      <c r="C19" s="20">
+        <v>10</v>
+      </c>
+      <c r="D19" s="20">
+        <v>10</v>
+      </c>
+      <c r="E19" s="20">
+        <v>11</v>
+      </c>
+      <c r="F19" s="21">
         <v>15.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="21">
-        <v>0</v>
-      </c>
-      <c r="C7" s="21">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>4</v>
-      </c>
-      <c r="G7" s="22">
-        <v>15</v>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="20">
+        <v>10</v>
+      </c>
+      <c r="C20" s="20">
+        <v>11</v>
+      </c>
+      <c r="D20" s="20">
+        <v>9</v>
+      </c>
+      <c r="E20" s="20">
+        <v>11</v>
+      </c>
+      <c r="F20" s="21">
+        <v>15.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="21">
-        <v>0</v>
-      </c>
-      <c r="C8" s="21">
-        <v>0</v>
-      </c>
-      <c r="D8" s="21">
-        <v>2</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21">
-        <v>4</v>
-      </c>
-      <c r="G8" s="22">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="21">
-        <v>0</v>
-      </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>1</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21">
-        <v>5</v>
-      </c>
-      <c r="G9" s="22">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="21">
-        <v>0</v>
-      </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>1</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21">
-        <v>4</v>
-      </c>
-      <c r="G10" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="21">
-        <v>0</v>
-      </c>
-      <c r="C11" s="21">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21">
-        <v>3</v>
-      </c>
-      <c r="G11" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="21">
-        <v>0</v>
-      </c>
-      <c r="C12" s="20">
-        <v>0</v>
-      </c>
-      <c r="D12" s="20">
-        <v>2</v>
-      </c>
-      <c r="E12" s="20">
-        <v>0</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4</v>
-      </c>
-      <c r="G12" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="21">
-        <v>0</v>
-      </c>
-      <c r="C13" s="21">
-        <v>0</v>
-      </c>
-      <c r="D13" s="21">
-        <v>2</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21">
-        <v>4</v>
-      </c>
-      <c r="G13" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="21">
-        <v>0</v>
-      </c>
-      <c r="C14" s="21">
-        <v>0</v>
-      </c>
-      <c r="D14" s="21">
-        <v>2</v>
-      </c>
-      <c r="E14" s="21">
-        <v>0</v>
-      </c>
-      <c r="F14" s="21">
-        <v>4</v>
-      </c>
-      <c r="G14" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="21">
-        <v>0</v>
-      </c>
-      <c r="C15" s="21">
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
-        <v>3</v>
-      </c>
-      <c r="G15" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="21">
-        <v>0</v>
-      </c>
-      <c r="C16" s="20">
-        <v>2</v>
-      </c>
-      <c r="D16" s="20">
-        <v>2</v>
-      </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
-      <c r="F16" s="20">
-        <v>5</v>
-      </c>
-      <c r="G16" s="22">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="21">
-        <v>0</v>
-      </c>
-      <c r="C17" s="21">
-        <v>0</v>
-      </c>
-      <c r="D17" s="21">
-        <v>1</v>
-      </c>
-      <c r="E17" s="21">
-        <v>0</v>
-      </c>
-      <c r="F17" s="21">
-        <v>4</v>
-      </c>
-      <c r="G17" s="22">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="21">
-        <v>0</v>
-      </c>
-      <c r="C18" s="21">
-        <v>0</v>
-      </c>
-      <c r="D18" s="21">
-        <v>1</v>
-      </c>
-      <c r="E18" s="21">
-        <v>0</v>
-      </c>
-      <c r="F18" s="21">
-        <v>4</v>
-      </c>
-      <c r="G18" s="22">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="21">
-        <v>10</v>
-      </c>
-      <c r="C19" s="21">
-        <v>10</v>
-      </c>
-      <c r="D19" s="21">
-        <v>10</v>
-      </c>
-      <c r="E19" s="21">
-        <v>11</v>
-      </c>
-      <c r="F19" s="21">
-        <v>4</v>
-      </c>
-      <c r="G19" s="22">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="B20" s="21">
-        <v>10</v>
-      </c>
-      <c r="C20" s="21">
-        <v>11</v>
-      </c>
-      <c r="D20" s="21">
-        <v>9</v>
-      </c>
-      <c r="E20" s="21">
-        <v>11</v>
-      </c>
-      <c r="F20" s="21">
-        <v>2</v>
-      </c>
-      <c r="G20" s="22">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
@@ -19473,16 +18775,13 @@
       <c r="E21" s="1">
         <v>11</v>
       </c>
-      <c r="F21" s="1">
-        <v>3</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="F21" s="18">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>56</v>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="B22" s="1">
         <v>11</v>
@@ -19496,16 +18795,13 @@
       <c r="E22" s="1">
         <v>9</v>
       </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="F22" s="18">
         <v>14.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>57</v>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
@@ -19519,16 +18815,13 @@
       <c r="E23" s="1">
         <v>11</v>
       </c>
-      <c r="F23" s="1">
-        <v>4</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="F23" s="18">
         <v>15.2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>58</v>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
@@ -19542,16 +18835,13 @@
       <c r="E24" s="1">
         <v>11</v>
       </c>
-      <c r="F24" s="1">
-        <v>3</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="F24" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>59</v>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="B25" s="1">
         <v>10</v>
@@ -19565,16 +18855,13 @@
       <c r="E25" s="1">
         <v>11</v>
       </c>
-      <c r="F25" s="1">
-        <v>2</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="F25" s="18">
         <v>15.2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>60</v>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
@@ -19588,16 +18875,13 @@
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="1">
-        <v>4</v>
-      </c>
-      <c r="G26" s="19">
+      <c r="F26" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>61</v>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
@@ -19611,16 +18895,13 @@
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="1">
-        <v>2</v>
-      </c>
-      <c r="G27" s="19">
+      <c r="F27" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>62</v>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
@@ -19634,16 +18915,13 @@
       <c r="E28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="1">
-        <v>4</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="F28" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>63</v>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
@@ -19657,16 +18935,13 @@
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1">
-        <v>4</v>
-      </c>
-      <c r="G29" s="19">
+      <c r="F29" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>64</v>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
@@ -19680,16 +18955,13 @@
       <c r="E30" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="1">
-        <v>3</v>
-      </c>
-      <c r="G30" s="19">
+      <c r="F30" s="18">
         <v>15.2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>65</v>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
@@ -19703,16 +18975,13 @@
       <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="1">
-        <v>4</v>
-      </c>
-      <c r="G31" s="19">
+      <c r="F31" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>66</v>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
@@ -19726,29 +18995,26 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="1">
-        <v>3</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="F32" s="18">
         <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62" s="14">
         <v>26.8514431641951</v>
       </c>
       <c r="C62" s="1">
@@ -19759,7 +19025,7 @@
       <c r="A63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63" s="14">
         <v>27.313000567495301</v>
       </c>
       <c r="C63" s="1">
@@ -19770,18 +19036,18 @@
       <c r="A64" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B64" s="15">
+      <c r="B64" s="14">
         <v>25.099800796022201</v>
       </c>
       <c r="C64" s="1">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65" s="14">
         <v>28.407745422683501</v>
       </c>
       <c r="C65" s="1">
@@ -19790,30 +19056,19 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B66" s="15">
-        <v>20.5182845286831</v>
-      </c>
-      <c r="C66" s="1">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="15">
+      <c r="B66" s="14">
         <v>82.682041580986606</v>
       </c>
-      <c r="C67" s="23">
+      <c r="C66" s="22">
         <v>452.8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
-      <sortCondition ref="G1"/>
+  <autoFilter ref="A1:F21" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+      <sortCondition ref="F1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -19824,7 +19079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F19D1F8-E0C0-4EE9-B316-914945355609}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
@@ -19832,12 +19087,11 @@
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -19854,15 +19108,12 @@
         <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>25</v>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
@@ -19879,13 +19130,10 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>4</v>
@@ -19900,15 +19148,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
         <v>15.1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -19922,16 +19167,13 @@
       <c r="E4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="F4" s="2">
         <v>14.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>16</v>
@@ -19945,16 +19187,13 @@
       <c r="E5" s="1">
         <v>16</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="F5" s="2">
         <v>15.9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>9</v>
@@ -19968,16 +19207,13 @@
       <c r="E6" s="1">
         <v>11</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="F6" s="2">
         <v>15.9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
@@ -19991,16 +19227,13 @@
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="F7" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>31</v>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
@@ -20014,29 +19247,26 @@
       <c r="E8" s="1">
         <v>7</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="F8" s="2">
         <v>15.6</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="C36" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="14">
         <v>20.445048300260801</v>
       </c>
       <c r="C37" s="1">
@@ -20047,7 +19277,7 @@
       <c r="A38" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="14">
         <v>24.5560583156173</v>
       </c>
       <c r="C38" s="1">
@@ -20058,7 +19288,7 @@
       <c r="A39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="14">
         <v>23.065125189341501</v>
       </c>
       <c r="C39" s="1">
@@ -20069,7 +19299,7 @@
       <c r="A40" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="14">
         <v>21.679483388678801</v>
       </c>
       <c r="C40" s="1">
@@ -20078,29 +19308,18 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="15">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B41" s="14">
         <v>37.951943296753498</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C41" s="17">
         <v>92.89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
+  <autoFilter ref="A1:F8" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F8">
       <sortCondition ref="A1:A8"/>
     </sortState>
   </autoFilter>
@@ -20112,7 +19331,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE05E8F-84CF-464F-9851-002DD2A6D98C}">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -20120,12 +19339,11 @@
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="2.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -20142,13 +19360,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -20167,256 +19382,223 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="20">
         <v>0</v>
       </c>
+      <c r="D3" s="20">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0</v>
+      </c>
+      <c r="F3" s="21">
+        <v>13.77</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B4" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="20">
+        <v>0</v>
+      </c>
+      <c r="D4" s="20">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0</v>
+      </c>
+      <c r="F4" s="20">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0</v>
+      </c>
+      <c r="D6" s="20">
+        <v>1</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>31.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="20">
+        <v>6</v>
+      </c>
+      <c r="C8" s="20">
+        <v>6</v>
+      </c>
+      <c r="D8" s="20">
+        <v>3</v>
+      </c>
+      <c r="E8" s="20">
+        <v>4</v>
+      </c>
+      <c r="F8" s="21">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="21">
-        <v>0</v>
-      </c>
-      <c r="D3" s="21">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21">
-        <v>0</v>
-      </c>
-      <c r="F3" s="21">
-        <v>1</v>
-      </c>
-      <c r="G3" s="22">
-        <v>13.77</v>
+      <c r="C9" s="20">
+        <v>6</v>
+      </c>
+      <c r="D9" s="20">
+        <v>3</v>
+      </c>
+      <c r="E9" s="20">
+        <v>4</v>
+      </c>
+      <c r="F9" s="21">
+        <v>11.33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="21" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="21">
-        <v>0</v>
-      </c>
-      <c r="D4" s="21">
-        <v>0</v>
-      </c>
-      <c r="E4" s="21">
-        <v>0</v>
-      </c>
-      <c r="F4" s="21">
-        <v>1</v>
-      </c>
-      <c r="G4" s="21">
-        <v>9.44</v>
+      <c r="C10" s="20">
+        <v>7</v>
+      </c>
+      <c r="D10" s="20">
+        <v>3</v>
+      </c>
+      <c r="E10" s="20">
+        <v>4</v>
+      </c>
+      <c r="F10" s="21">
+        <v>26.66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="21" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="21">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21">
-        <v>0</v>
-      </c>
-      <c r="E5" s="21">
-        <v>0</v>
-      </c>
-      <c r="F5" s="21">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>6.66</v>
+      <c r="C11" s="20">
+        <v>6</v>
+      </c>
+      <c r="D11" s="20">
+        <v>3</v>
+      </c>
+      <c r="E11" s="20">
+        <v>4</v>
+      </c>
+      <c r="F11" s="21">
+        <v>28.88</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="21" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="21">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21">
-        <v>0</v>
-      </c>
-      <c r="F6" s="21">
-        <v>1</v>
-      </c>
-      <c r="G6" s="22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="21">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21">
-        <v>1</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22">
-        <v>31.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="21">
-        <v>6</v>
-      </c>
-      <c r="C8" s="21">
-        <v>6</v>
-      </c>
-      <c r="D8" s="21">
-        <v>3</v>
-      </c>
-      <c r="E8" s="21">
+      <c r="C12" s="19">
+        <v>7</v>
+      </c>
+      <c r="D12" s="19">
         <v>4</v>
       </c>
-      <c r="F8" s="21">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22">
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="21">
-        <v>6</v>
-      </c>
-      <c r="D9" s="21">
-        <v>3</v>
-      </c>
-      <c r="E9" s="21">
+      <c r="E12" s="19">
         <v>4</v>
       </c>
-      <c r="F9" s="21">
-        <v>1</v>
-      </c>
-      <c r="G9" s="22">
-        <v>11.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="21">
-        <v>7</v>
-      </c>
-      <c r="D10" s="21">
-        <v>3</v>
-      </c>
-      <c r="E10" s="21">
-        <v>4</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22">
-        <v>26.66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="21">
-        <v>6</v>
-      </c>
-      <c r="D11" s="21">
-        <v>3</v>
-      </c>
-      <c r="E11" s="21">
-        <v>4</v>
-      </c>
-      <c r="F11" s="21">
-        <v>1</v>
-      </c>
-      <c r="G11" s="22">
-        <v>28.88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="20">
-        <v>7</v>
-      </c>
-      <c r="D12" s="20">
-        <v>4</v>
-      </c>
-      <c r="E12" s="20">
-        <v>4</v>
-      </c>
       <c r="F12" s="21">
-        <v>1</v>
-      </c>
-      <c r="G12" s="22">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="14">
         <v>13.4164078649987</v>
       </c>
       <c r="C43" s="1">
@@ -20427,7 +19609,7 @@
       <c r="A44" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="14">
         <v>14.3527000944073</v>
       </c>
       <c r="C44" s="1">
@@ -20438,7 +19620,7 @@
       <c r="A45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="14">
         <v>7.3484692283495301</v>
       </c>
       <c r="C45" s="1">
@@ -20449,7 +19631,7 @@
       <c r="A46" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="14">
         <v>8.9442719099991592</v>
       </c>
       <c r="C46" s="1">
@@ -20458,30 +19640,19 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="15">
-        <v>2.6457513110645898</v>
-      </c>
-      <c r="C47" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B47" s="14">
         <v>75.970080294810799</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C47" s="23">
         <v>202.25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G12">
-      <sortCondition ref="G1"/>
+  <autoFilter ref="A1:F12" xr:uid="{46215D94-257C-4C1A-A4CB-D51E27942313}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F12">
+      <sortCondition ref="F1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
